--- a/04_Figures/F01/c_data/F01_data.xlsx
+++ b/04_Figures/F01/c_data/F01_data.xlsx
@@ -654,7 +654,7 @@
     <t xml:space="preserve">Participant ids</t>
   </si>
   <si>
-    <t xml:space="preserve">Participant is the proteomics sample label. Parent_ID is the participant number inside the parent trial workbook, at 00_input/parent_meta/&lt;Parent_trial&gt;.xlsx.</t>
+    <t xml:space="preserve">Participant is the proteomics sample label. Parent_ID is the participant number in the parent trial; 00_input/parent_trials.csv lists each trial's arms and participant counts.</t>
   </si>
   <si>
     <t xml:space="preserve">Source</t>
